--- a/data/trans_dic/P13A_1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_2023-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,63; 100,0</t>
+          <t>42,51; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,63; 100,0</t>
+          <t>42,51; 100,0</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,46; 100,0</t>
+          <t>55,28; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,9; 100,0</t>
+          <t>64,48; 100,0</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93,78; 100,0</t>
+          <t>77,51; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,79; 100,0</t>
+          <t>85,58; 100,0</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,68; 100,0</t>
+          <t>87,95; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,95; 100,0</t>
+          <t>89,83; 100,0</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,69; 100,0</t>
+          <t>91,44; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93,21; 100,0</t>
+          <t>92,44; 100,0</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85,6; 100,0</t>
+          <t>86,55; 100,0</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,46; 97,41</t>
+          <t>88,96; 97,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,82; 97,98</t>
+          <t>90,62; 97,63</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>16059</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5707; 16480</t>
+          <t>8436; 19847</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5707; 16480</t>
+          <t>8436; 19847</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>14327</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3304; 8819</t>
+          <t>5529; 10003</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8336; 13253</t>
+          <t>9934; 15406</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>25865</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16562; 17660</t>
+          <t>15233; 19652</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23849; 24639</t>
+          <t>22914; 26774</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>41032</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>48423</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37723; 43025</t>
+          <t>37362; 42479</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45712; 50259</t>
+          <t>44798; 49870</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>32439</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>43455</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27586; 30418</t>
+          <t>30476; 33328</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37845; 40601</t>
+          <t>40992; 44344</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21714</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>25145</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15626; 19024</t>
+          <t>17560; 21377</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20236; 23642</t>
+          <t>22780; 26319</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>155080</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134306; 147895</t>
+          <t>146218; 159931</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>171861; 185399</t>
+          <t>185120; 199435</t>
         </is>
       </c>
     </row>
